--- a/Department_BillableData_Security Testing.xlsx
+++ b/Department_BillableData_Security Testing.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Billable Type</t>
   </si>
@@ -26,7 +26,10 @@
     <t>Bench</t>
   </si>
   <si>
-    <t>TNM</t>
+    <t>InternalRNDProducts</t>
+  </si>
+  <si>
+    <t>Shadow</t>
   </si>
 </sst>
 </file>
@@ -111,10 +114,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="12.625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.328125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="19.0859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -147,6 +150,14 @@
         <v>5.0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A2:B2"/>

--- a/Department_BillableData_Security Testing.xlsx
+++ b/Department_BillableData_Security Testing.xlsx
@@ -29,7 +29,7 @@
     <t>InternalRNDProducts</t>
   </si>
   <si>
-    <t>Shadow</t>
+    <t>TNM</t>
   </si>
 </sst>
 </file>
